--- a/check_in_forms/042_child_support_office_check_in_form--check_in_forms.xlsx
+++ b/check_in_forms/042_child_support_office_check_in_form--check_in_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,8 +835,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,12 +864,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'scheduled_appointment',_'value':_'appointment'}</t>
+          <t>scheduled_appointment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Scheduled Appointment', 'value': 'appointment'}</t>
+          <t>Scheduled Appointment</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'walk-in_inquiry',_'value':_'walkin'}</t>
+          <t>walk-in_inquiry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Walk-in Inquiry', 'value': 'walkin'}</t>
+          <t>Walk-in Inquiry</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'dropping_off_documents',_'value':_'documents'}</t>
+          <t>dropping_off_documents</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Dropping off Documents', 'value': 'documents'}</t>
+          <t>Dropping off Documents</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'payment_assistance',_'value':_'payment'}</t>
+          <t>payment_assistance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Payment Assistance', 'value': 'payment'}</t>
+          <t>Payment Assistance</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'phone_call',_'value':_'phone'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Phone Call', 'value': 'phone'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'email_update',_'value':_'email'}</t>
+          <t>email_update</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Email Update', 'value': 'email'}</t>
+          <t>Email Update</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'standard_mail',_'value':_'mail'}</t>
+          <t>standard_mail</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Standard Mail', 'value': 'mail'}</t>
+          <t>Standard Mail</t>
         </is>
       </c>
     </row>
